--- a/12_Типовые_решения/Типовые_решения.xlsx
+++ b/12_Типовые_решения/Типовые_решения.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Типовые решения" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Типовые решения'!$A$1:$F$8</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Типовые решения'!$A$1:$F$12</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="72">
   <si>
     <t xml:space="preserve">Код</t>
   </si>
@@ -167,6 +167,78 @@
   </si>
   <si>
     <t xml:space="preserve">НСП-007, СТД-003, ЭНЦ-003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">РЕШ-008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Очистка ТЭН от накипи</t>
+  </si>
+  <si>
+    <t xml:space="preserve">НСП-008 Накипеобразование на ТЭН</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1) Полностью обесточить котёл, проверить отсутствие напряжения (см. РГЛ-004, раздел 4). 2) Демонтировать ТЭН. 3) Выполнить химическую или механическую очистку поверхности от накипи. 4) Проверить сопротивление изоляции перед установкой. 5) Установить ТЭН обратно, выполнить пробное включение и сверить время выхода на температуру с нормой СТД-004.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Средства для химической очистки от накипи, совместимые с материалом ТЭН, мегаомметр, стандартный электромонтажный инструмент</t>
+  </si>
+  <si>
+    <t xml:space="preserve">НСП-008, СТД-004, РГЛ-004, ЭНЦ-004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">РЕШ-009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Замена ТЭН при пробое изоляции</t>
+  </si>
+  <si>
+    <t xml:space="preserve">НСП-009 Утечка тока / повреждение изоляции ТЭН</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1) Немедленно отключить котёл, не пытаться повторно включить (см. СТД-004, раздел 4). 2) Обесточить, проверить отсутствие напряжения. 3) Демонтировать повреждённый ТЭН. 4) Установить новый ТЭН соответствующего типоразмера по паспорту. 5) Проверить сопротивление изоляции нового элемента и срабатывание УЗО перед вводом в эксплуатацию.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Новый ТЭН соответствующего типоразмера (по паспорту котла), мегаомметр, указатель напряжения</t>
+  </si>
+  <si>
+    <t xml:space="preserve">НСП-009, СТД-004, РГЛ-004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">РЕШ-010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Очистка колосниковой решётки от шлака</t>
+  </si>
+  <si>
+    <t xml:space="preserve">НСП-010 Зашлаковывание колосниковой решётки</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1) Остановить котёл, дать прогореть остаткам топлива и остыть золе (см. РГЛ-005, раздел 3). 2) Механически удалить шлак с колосниковой решётки, не повреждая саму решётку. 3) Проверить свободный проход воздуха через решётку. 4) После розжига проверить тягу и сверить с нормой СТД-005.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Скребки и щётки для очистки колосниковой решётки, средства защиты органов дыхания</t>
+  </si>
+  <si>
+    <t xml:space="preserve">НСП-010, СТД-005, РГЛ-005, ЭНЦ-005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">РЕШ-011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Прочистка дымохода и проверка тяги</t>
+  </si>
+  <si>
+    <t xml:space="preserve">НСП-011 Недостаточная тяга (засорение дымохода)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1) Остановить котёл, дать остыть. 2) Выполнить механическую прочистку дымохода от сажи гибким тросом/ёршом с учётом требований пожарной безопасности. 3) Проверить дымоход на отсутствие посторонних предметов и целостность. 4) После розжига проверить тягу тягомером и сверить с нормой СТД-005.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Гибкий трос/ёрш для очистки дымохода, тягомер, средства индивидуальной защиты</t>
+  </si>
+  <si>
+    <t xml:space="preserve">НСП-011, СТД-005, РГЛ-005, ЭНЦ-005</t>
   </si>
 </sst>
 </file>
@@ -277,16 +349,20 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -571,179 +647,259 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="55"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="26"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="82.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+    <row r="2" customFormat="false" ht="81.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+    <row r="3" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
+    <row r="4" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="82.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
+    <row r="5" customFormat="false" ht="81.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="108.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
+    <row r="6" customFormat="false" ht="108.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="3" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="82.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
+    <row r="7" customFormat="false" ht="81.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F7" s="3" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="82.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
+    <row r="8" customFormat="false" ht="81.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="F8" s="3" t="s">
         <v>47</v>
       </c>
     </row>
+    <row r="9" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="82.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F8"/>
+  <autoFilter ref="A1:F12"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
